--- a/files/港岛-北角-海璇 II.xlsx
+++ b/files/港岛-北角-海璇 II.xlsx
@@ -7274,7 +7274,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2024-11-24</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -7472,7 +7472,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -7604,7 +7604,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -7802,7 +7802,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -8000,7 +8000,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -8198,7 +8198,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -8264,7 +8264,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -8330,7 +8330,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-27</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -8462,7 +8462,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -8594,7 +8594,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-27</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -8660,7 +8660,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -8726,7 +8726,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -8858,7 +8858,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -8990,7 +8990,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -9056,7 +9056,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -9188,7 +9188,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -10339,7 +10339,7 @@
           <t>A | 2080呎 (4+房)
 $12000万
 $57,692/呎
-(24年-11月-24日)</t>
+(24年-11月-25日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -10355,7 +10355,7 @@
           <t>A | 2073呎 (4+房)
 $12173万
 $58,721/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr"/>
@@ -10371,7 +10371,7 @@
           <t>A | 1448呎 (4+房)
 $7162万
 $49,459/呎
-(25年-12月-02日)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -10379,7 +10379,7 @@
           <t>B | 1111呎 (3房)
 $5500万
 $49,505/呎
-(25年-05月-08日)</t>
+(25年-05月-09日)</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
           <t>A | 1448呎 (4+房)
 $5636万
 $38,925/呎
-(24年-10月-06日)</t>
+(24年-10月-07日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -10402,7 +10402,7 @@
           <t>B | 1111呎 (3房)
 $4389万
 $39,505/呎
-(24年-10月-03日)</t>
+(24年-10月-04日)</t>
         </is>
       </c>
     </row>
@@ -10417,7 +10417,7 @@
           <t>A | 1448呎 (4+房)
 $5431万
 $37,506/呎
-(24年-10月-07日)</t>
+(24年-10月-08日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -10425,7 +10425,7 @@
           <t>B | 1111呎 (3房)
 $4536万
 $40,830/呎
-(24年-10月-07日)</t>
+(24年-10月-08日)</t>
         </is>
       </c>
     </row>
@@ -10440,7 +10440,7 @@
           <t>A | 1492呎 (4+房)
 $5939万
 $39,805/呎
-(24年-09月-16日)</t>
+(24年-09月-17日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -10448,7 +10448,7 @@
           <t>B | 1155呎 (3房)
 $4572万
 $39,586/呎
-(24年-10月-13日)</t>
+(24年-10月-14日)</t>
         </is>
       </c>
     </row>
@@ -10463,7 +10463,7 @@
           <t>A | 1448呎 (4+房)
 $5200万
 $35,912/呎
-(24年-10月-06日)</t>
+(24年-10月-07日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -10471,7 +10471,7 @@
           <t>B | 1111呎 (3房)
 $4538万
 $40,846/呎
-(24年-10月-03日)</t>
+(24年-10月-04日)</t>
         </is>
       </c>
     </row>
@@ -10486,7 +10486,7 @@
           <t>A | 1448呎 (4+房)
 $5148万
 $35,552/呎
-(24年-09月-23日)</t>
+(24年-09月-24日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -10494,7 +10494,7 @@
           <t>B | 1111呎 (3房)
 $4307万
 $38,765/呎
-(24年-09月-22日)</t>
+(24年-09月-23日)</t>
         </is>
       </c>
     </row>
@@ -10509,7 +10509,7 @@
           <t>A | 1448呎 (4+房)
 $5230万
 $36,119/呎
-(24年-10月-08日)</t>
+(24年-10月-09日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -10517,7 +10517,7 @@
           <t>B | 1111呎 (3房)
 $4100万
 $36,906/呎
-(24年-10月-07日)</t>
+(24年-10月-08日)</t>
         </is>
       </c>
     </row>
@@ -10532,7 +10532,7 @@
           <t>A | 1448呎 (4+房)
 $4987万
 $34,439/呎
-(24年-09月-18日)</t>
+(24年-09月-19日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -10540,7 +10540,7 @@
           <t>B | 1111呎 (3房)
 $4166万
 $37,496/呎
-(24年-09月-26日)</t>
+(24年-09月-27日)</t>
         </is>
       </c>
     </row>
@@ -10555,7 +10555,7 @@
           <t>A | 1448呎 (4+房)
 $5153万
 $35,586/呎
-(24年-10月-17日)</t>
+(24年-10月-18日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -10563,7 +10563,7 @@
           <t>B | 1111呎 (3房)
 $3962万
 $35,658/呎
-(24年-10月-29日)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
     </row>
@@ -10578,7 +10578,7 @@
           <t>A | 1448呎 (4+房)
 $4819万
 $33,281/呎
-(24年-10月-02日)</t>
+(24年-10月-03日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -10586,7 +10586,7 @@
           <t>B | 1111呎 (3房)
 $3904万
 $35,139/呎
-(24年-09月-26日)</t>
+(24年-09月-27日)</t>
         </is>
       </c>
     </row>
@@ -10601,7 +10601,7 @@
           <t>A | 1448呎 (4+房)
 $4780万
 $33,011/呎
-(24年-10月-03日)</t>
+(24年-10月-04日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -10609,7 +10609,7 @@
           <t>B | 1111呎 (3房)
 $3869万
 $34,827/呎
-(24年-09月-15日)</t>
+(24年-09月-16日)</t>
         </is>
       </c>
     </row>
@@ -10624,7 +10624,7 @@
           <t>A | 1448呎 (4+房)
 $5168万
 $35,691/呎
-(24年-10月-15日)</t>
+(24年-10月-16日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -10632,7 +10632,7 @@
           <t>B | 1111呎 (3房)
 $3765万
 $33,891/呎
-(24年-09月-22日)</t>
+(24年-09月-23日)</t>
         </is>
       </c>
     </row>
@@ -10647,7 +10647,7 @@
           <t>A | 1448呎 (4+房)
 $4940万
 $34,116/呎
-(24年-10月-20日)</t>
+(24年-10月-21日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -10655,7 +10655,7 @@
           <t>B | 1111呎 (3房)
 $3825万
 $34,432/呎
-(24年-09月-24日)</t>
+(24年-09月-25日)</t>
         </is>
       </c>
     </row>
@@ -10670,7 +10670,7 @@
           <t>A | 1432呎 (4+房)
 $4649万
 $32,468/呎
-(25年-05月-08日)</t>
+(25年-05月-09日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -10678,7 +10678,7 @@
           <t>B | 1095呎 (3房)
 $4278万
 $39,068/呎
-(24年-11月-17日)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
     </row>
